--- a/mistral_translate_work/split_by_prompt/excel/name_title/lang_multi_text/lang_multi_text__name_title__part_0111.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/name_title/lang_multi_text/lang_multi_text__name_title__part_0111.xlsx
@@ -32844,7 +32844,7 @@
       </c>
       <c r="M463" t="inlineStr">
         <is>
-          <t>Khúc Ca Về Người Tử Đạo Vô Danh</t>
+          <t>Khúc Ca Vị Thánh Vô Danh</t>
         </is>
       </c>
       <c r="N463" t="inlineStr">
@@ -32914,7 +32914,7 @@
       </c>
       <c r="M464" t="inlineStr">
         <is>
-          <t>Nhạc nền trong trận chiến với Lady of the Sea</t>
+          <t>Nhạc nền trong trận chiến với Lady of the Sea.</t>
         </is>
       </c>
       <c r="N464" t="inlineStr">
@@ -33054,7 +33054,7 @@
       </c>
       <c r="M466" t="inlineStr">
         <is>
-          <t>Nhạc nền khi lần đầu đến Septimont</t>
+          <t>Nhạc nền khi lần đầu đặt chân đến Septimont</t>
         </is>
       </c>
       <c r="N466" t="inlineStr">
@@ -33124,7 +33124,7 @@
       </c>
       <c r="M467" t="inlineStr">
         <is>
-          <t>Lời Thì Thầm Của Những Vì Sao</t>
+          <t>Lời thì thầm của những vì sao</t>
         </is>
       </c>
       <c r="N467" t="inlineStr">
@@ -33194,7 +33194,7 @@
       </c>
       <c r="M468" t="inlineStr">
         <is>
-          <t>Nhạc nền cho Central Hub</t>
+          <t>Nhạc nền tại Trung Tâm Điều Hành</t>
         </is>
       </c>
       <c r="N468" t="inlineStr">
@@ -33264,7 +33264,7 @@
       </c>
       <c r="M469" t="inlineStr">
         <is>
-          <t>Bài Ca Bất Khuất</t>
+          <t>Khúc Ca Bất Khuất</t>
         </is>
       </c>
       <c r="N469" t="inlineStr">
@@ -33334,7 +33334,7 @@
       </c>
       <c r="M470" t="inlineStr">
         <is>
-          <t>Nhạc nền trong Nhiệm Vụ Thám Hiểm "Khi Bầu Trời Chứng Kiến Cuộc Gặp Gỡ Của Chúng Ta"</t>
+          <t>Nhạc nền trong Nhiệm Vụ Khám Phá "Khi Bầu Trời Chứng Kiến Cuộc Gặp Gỡ Của Ta".</t>
         </is>
       </c>
       <c r="N470" t="inlineStr">
@@ -33404,7 +33404,7 @@
       </c>
       <c r="M471" t="inlineStr">
         <is>
-          <t>A Blazing Star's Soliloquy</t>
+          <t>Độc Thoại Của Ngôi Sao Cháy</t>
         </is>
       </c>
       <c r="N471" t="inlineStr">
@@ -33474,7 +33474,7 @@
       </c>
       <c r="M472" t="inlineStr">
         <is>
-          <t>Windswept Watch</t>
+          <t>Tháp Gió Cuốn</t>
         </is>
       </c>
       <c r="N472" t="inlineStr">
@@ -33544,7 +33544,7 @@
       </c>
       <c r="M473" t="inlineStr">
         <is>
-          <t>Lễ Tang Của Vương Quốc Đổ Nát</t>
+          <t>Đám Tang Của Vương Quốc Vỡ</t>
         </is>
       </c>
       <c r="N473" t="inlineStr">
@@ -33614,7 +33614,7 @@
       </c>
       <c r="M474" t="inlineStr">
         <is>
-          <t>Vùng Đất Héo Úa Vô Danh</t>
+          <t>Vùng Đất Tàn Phế Vô Danh</t>
         </is>
       </c>
       <c r="N474" t="inlineStr">
@@ -33684,7 +33684,7 @@
       </c>
       <c r="M475" t="inlineStr">
         <is>
-          <t>Nếu Ta Có Thể Đan Nối Định Mệnh</t>
+          <t>Nếu Ta Có Thể Dệt Nên Định Mệnh</t>
         </is>
       </c>
       <c r="N475" t="inlineStr">
@@ -33754,7 +33754,7 @@
       </c>
       <c r="M476" t="inlineStr">
         <is>
-          <t>Trở Về Vòng Tay Asphodel</t>
+          <t>Quay về Asphodel's Embrace</t>
         </is>
       </c>
       <c r="N476" t="inlineStr">
@@ -33824,7 +33824,7 @@
       </c>
       <c r="M477" t="inlineStr">
         <is>
-          <t>O Sun, Witness My Name</t>
+          <t>Hỡi Mặt Trời, Xin Chứng Kiến Danh Ta</t>
         </is>
       </c>
       <c r="N477" t="inlineStr">
@@ -33894,7 +33894,7 @@
       </c>
       <c r="M478" t="inlineStr">
         <is>
-          <t>Hãy Chôn Ta Trong Ánh Nắng</t>
+          <t>Chôn Ta Trong Ánh Nắng</t>
         </is>
       </c>
       <c r="N478" t="inlineStr">
@@ -34034,7 +34034,7 @@
       </c>
       <c r="M480" t="inlineStr">
         <is>
-          <t>In Moments Does Moon Persist</t>
+          <t>Ánh Trăng Vẫn Ở Đó Trong Khoảnh Khắc</t>
         </is>
       </c>
       <c r="N480" t="inlineStr">
@@ -34104,7 +34104,7 @@
       </c>
       <c r="M481" t="inlineStr">
         <is>
-          <t>Nhạc nền khi tạm biệt Qiuyuan ở Ragunna</t>
+          <t>Nhạc nền khi chia tay Qiuyuan tại Ragunna.</t>
         </is>
       </c>
       <c r="N481" t="inlineStr">
@@ -34174,7 +34174,7 @@
       </c>
       <c r="M482" t="inlineStr">
         <is>
-          <t>Gian Nan Của Thanh Kiếm Thép</t>
+          <t>Gian Truân Kiếm Thép</t>
         </is>
       </c>
       <c r="N482" t="inlineStr">
@@ -34244,7 +34244,7 @@
       </c>
       <c r="M483" t="inlineStr">
         <is>
-          <t>Till Dawn</t>
+          <t>Cho Đến Bình Minh</t>
         </is>
       </c>
       <c r="N483" t="inlineStr">
@@ -34314,7 +34314,7 @@
       </c>
       <c r="M484" t="inlineStr">
         <is>
-          <t>Firebound Angel</t>
+          <t>Thiên Thần Lửa</t>
         </is>
       </c>
       <c r="N484" t="inlineStr">
@@ -34384,7 +34384,7 @@
       </c>
       <c r="M485" t="inlineStr">
         <is>
-          <t>Lingering Summer Light</t>
+          <t>Ánh Hạ Lưu Quang</t>
         </is>
       </c>
       <c r="N485" t="inlineStr">
@@ -34454,7 +34454,7 @@
       </c>
       <c r="M486" t="inlineStr">
         <is>
-          <t>Tangled Flower</t>
+          <t>Bông Hoa Rối Loạn</t>
         </is>
       </c>
       <c r="N486" t="inlineStr">
@@ -34524,7 +34524,7 @@
       </c>
       <c r="M487" t="inlineStr">
         <is>
-          <t>Hướng Tới Kết Thúc</t>
+          <t>Hướng Về Kết Cục</t>
         </is>
       </c>
       <c r="N487" t="inlineStr">
@@ -34594,7 +34594,7 @@
       </c>
       <c r="M488" t="inlineStr">
         <is>
-          <t>Trước Khi Ve Kêu Tắt Lặng</t>
+          <t>Trước khi Tiếng Ve Tàn Phai</t>
         </is>
       </c>
       <c r="N488" t="inlineStr">
@@ -34664,7 +34664,7 @@
       </c>
       <c r="M489" t="inlineStr">
         <is>
-          <t>Collapsing Dawn</t>
+          <t>Bình Minh Sụp Đổ</t>
         </is>
       </c>
       <c r="N489" t="inlineStr">
@@ -34734,7 +34734,7 @@
       </c>
       <c r="M490" t="inlineStr">
         <is>
-          <t>Unfolding Chaos</t>
+          <t>Hỗn Độn Bùng Nổ</t>
         </is>
       </c>
       <c r="N490" t="inlineStr">
@@ -34804,7 +34804,7 @@
       </c>
       <c r="M491" t="inlineStr">
         <is>
-          <t>Khi Em Nắm Giữ Sự Thật</t>
+          <t>Khi Ta Nắm Giữ Chân Lý</t>
         </is>
       </c>
       <c r="N491" t="inlineStr">
@@ -34874,7 +34874,7 @@
       </c>
       <c r="M492" t="inlineStr">
         <is>
-          <t>Unfinished Journey</t>
+          <t>Hành trình dang dở</t>
         </is>
       </c>
       <c r="N492" t="inlineStr">
@@ -34944,7 +34944,7 @@
       </c>
       <c r="M493" t="inlineStr">
         <is>
-          <t>Khám Phá Những Điều Chưa Biết</t>
+          <t>Bước vào Vùng Đất Vô Định</t>
         </is>
       </c>
       <c r="N493" t="inlineStr">
@@ -35014,7 +35014,7 @@
       </c>
       <c r="M494" t="inlineStr">
         <is>
-          <t>Khoảnh Khắc Giữa Các Vì Sao</t>
+          <t>Khoảnh khắc giữa muôn vì sao</t>
         </is>
       </c>
       <c r="N494" t="inlineStr">
@@ -35084,7 +35084,7 @@
       </c>
       <c r="M495" t="inlineStr">
         <is>
-          <t>Ready Biker One</t>
+          <t>Xe Một sẵn sàng</t>
         </is>
       </c>
       <c r="N495" t="inlineStr">
@@ -35154,7 +35154,7 @@
       </c>
       <c r="M496" t="inlineStr">
         <is>
-          <t>Pioneer's Roadtrip Mix</t>
+          <t>Bản Mix Du Hành Tiên Phong</t>
         </is>
       </c>
       <c r="N496" t="inlineStr">
@@ -35224,7 +35224,7 @@
       </c>
       <c r="M497" t="inlineStr">
         <is>
-          <t>Our Torch, The Stars</t>
+          <t>Ngọn Đuốc của chúng ta, Những Vì Sao</t>
         </is>
       </c>
       <c r="N497" t="inlineStr">
@@ -35294,7 +35294,7 @@
       </c>
       <c r="M498" t="inlineStr">
         <is>
-          <t>Persona 5 Royal: Collab Album</t>
+          <t>Album Hợp Tác: Persona 5 Royal</t>
         </is>
       </c>
       <c r="N498" t="inlineStr">
@@ -35364,7 +35364,7 @@
       </c>
       <c r="M499" t="inlineStr">
         <is>
-          <t>Persona 3 Reload: Collab Album</t>
+          <t>Album Hợp Tác: Persona 3 Reload</t>
         </is>
       </c>
       <c r="N499" t="inlineStr">
@@ -35434,7 +35434,7 @@
       </c>
       <c r="M500" t="inlineStr">
         <is>
-          <t>Sonic the Hedgehog: Collab Album</t>
+          <t>Sonic the Hedgehog: Album Hợp Tác</t>
         </is>
       </c>
       <c r="N500" t="inlineStr">
@@ -35504,7 +35504,7 @@
       </c>
       <c r="M501" t="inlineStr">
         <is>
-          <t>For Ya</t>
+          <t>Vì Ya</t>
         </is>
       </c>
       <c r="N501" t="inlineStr">
